--- a/results/ARI.xlsx
+++ b/results/ARI.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\427消融实验版\SECT-a-new-method-based-on-louvain-main\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\Desktop\结果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2170100E-80FC-4BDB-880C-8CBF9278711B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="0" windowWidth="10520" windowHeight="7420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,7 +81,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -451,17 +450,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.08203125" customWidth="1"/>
-    <col min="2" max="2" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -492,7 +488,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>2.8799999999999999E-2</v>
+        <v>2.9766999999999998E-2</v>
       </c>
       <c r="C2" s="2">
         <v>0.95663799999999999</v>
@@ -501,13 +497,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>0.56218800000000002</v>
+        <v>0.58568200000000004</v>
       </c>
       <c r="F2" s="2">
-        <v>0.461177</v>
+        <v>0.45102100000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>0.112022</v>
+        <v>0.116325</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -521,16 +517,16 @@
         <v>0.73067800000000005</v>
       </c>
       <c r="D3" s="1">
-        <v>1</v>
+        <v>0.99185999999999996</v>
       </c>
       <c r="E3" s="1">
-        <v>0.27398499999999998</v>
+        <v>0.27973799999999999</v>
       </c>
       <c r="F3" s="1">
-        <v>0.39661200000000002</v>
+        <v>0.39645000000000002</v>
       </c>
       <c r="G3" s="1">
-        <v>5.4204000000000002E-2</v>
+        <v>5.2838000000000003E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -541,7 +537,7 @@
         <v>-0.165161</v>
       </c>
       <c r="C4" s="1">
-        <v>5.9297000000000002E-2</v>
+        <v>6.0987E-2</v>
       </c>
       <c r="D4" s="1">
         <v>-6.1989999999999996E-3</v>
@@ -553,7 +549,7 @@
         <v>1.4839E-2</v>
       </c>
       <c r="G4" s="1">
-        <v>-9.6790000000000001E-3</v>
+        <v>-1.0682000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -561,7 +557,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>1.1063999999999999E-2</v>
+        <v>1.3627E-2</v>
       </c>
       <c r="C5" s="1">
         <v>0.73067800000000005</v>
@@ -570,13 +566,13 @@
         <v>0.99185999999999996</v>
       </c>
       <c r="E5" s="1">
-        <v>0.28200500000000001</v>
+        <v>0.28811500000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>0.39679399999999998</v>
+        <v>0.38489000000000001</v>
       </c>
       <c r="G5" s="1">
-        <v>5.7361000000000002E-2</v>
+        <v>5.3055999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -599,7 +595,7 @@
         <v>0.419989</v>
       </c>
       <c r="G6" s="1">
-        <v>4.1313999999999997E-2</v>
+        <v>1.7628000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -645,7 +641,7 @@
         <v>0.433917</v>
       </c>
       <c r="G8" s="1">
-        <v>4.5920000000000002E-2</v>
+        <v>4.3490000000000001E-2</v>
       </c>
     </row>
   </sheetData>
